--- a/Result/profitability/3259.xlsx
+++ b/Result/profitability/3259.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.64125</v>
+        <v>-0.63875</v>
       </c>
       <c r="N2" t="n">
-        <v>14.4975</v>
+        <v>13.35875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7375</v>
+        <v>-0.7175</v>
       </c>
       <c r="N3" t="n">
-        <v>12.86625</v>
+        <v>12.90375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.71</v>
+        <v>-0.7175</v>
       </c>
       <c r="N4" t="n">
-        <v>14.6</v>
+        <v>13.7775</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.67375</v>
       </c>
       <c r="N5" t="n">
-        <v>15.90875</v>
+        <v>16.3075</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.58</v>
+        <v>-0.58375</v>
       </c>
       <c r="N6" t="n">
-        <v>19.28</v>
+        <v>19.19375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.52125</v>
+        <v>-0.51125</v>
       </c>
       <c r="N7" t="n">
-        <v>21.92</v>
+        <v>21.2375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.41625</v>
+        <v>-0.4125</v>
       </c>
       <c r="N8" t="n">
-        <v>24.33125</v>
+        <v>23.58</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.31</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>26.22</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>59</v>
+      </c>
+      <c r="D75" t="n">
+        <v>54</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-66.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.6062500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.805</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.01</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3811033608116677</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09000000000000008</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.1363636363636365</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4855403348554033</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
